--- a/src/attributions/attributions_saliency_traj_483.xlsx
+++ b/src/attributions/attributions_saliency_traj_483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,2278 +999,5692 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1642130017280579</v>
+        <v>0.008860863745212555</v>
       </c>
       <c r="B2" t="n">
-        <v>1.005849599838257</v>
+        <v>0.03123071789741516</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1457641124725342</v>
+        <v>0.01106877066195011</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2003367096185684</v>
+        <v>0.01768328435719013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1100818663835526</v>
+        <v>0.001944336108863354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03072944283485413</v>
+        <v>0.01804054714739323</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01023873221129179</v>
+        <v>0.006017160601913929</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000884839566424489</v>
+        <v>0.004600191954523325</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0220673531293869</v>
+        <v>0.00273366435430944</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03396310657262802</v>
+        <v>0.003813337301835418</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8367167711257935</v>
+        <v>0.03349619358778</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05348929762840271</v>
+        <v>0.01837458834052086</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3972688019275665</v>
+        <v>0.02343522012233734</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02726081199944019</v>
+        <v>0.007219256833195686</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2228191792964935</v>
+        <v>0.01773689314723015</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01887179166078568</v>
+        <v>0.006015435326844454</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05048611015081406</v>
+        <v>0.00734776072204113</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06875565648078918</v>
+        <v>0.00396121758967638</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06074972450733185</v>
+        <v>0.001926312455907464</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1387526094913483</v>
+        <v>0.005085499957203865</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0921928808093071</v>
+        <v>8.733547292649746e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006706850603222847</v>
+        <v>0.0003085384960286319</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1653628945350647</v>
+        <v>0.004197851289063692</v>
       </c>
       <c r="X2" t="n">
-        <v>0.006393354386091232</v>
+        <v>0.005385177209973335</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008027276955544949</v>
+        <v>0.003205865621566772</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06145896762609482</v>
+        <v>0.0008991147624328732</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03367664664983749</v>
+        <v>0.001642407034523785</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2265065759420395</v>
+        <v>0.002036373829469085</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1279914975166321</v>
+        <v>0.01070795021951199</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.04868919774889946</v>
+        <v>0.002492581028491259</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1280151307582855</v>
+        <v>0.004432648420333862</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.07143883407115936</v>
+        <v>0.007564000319689512</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.06222497671842575</v>
+        <v>0.00924394279718399</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.008484743535518646</v>
+        <v>0.00257465522736311</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.03856579586863518</v>
+        <v>0.002676820382475853</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03664637356996536</v>
+        <v>0.001087892567738891</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01990536414086819</v>
+        <v>0.0004756442504003644</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06242392212152481</v>
+        <v>0.006776762660592794</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.05332819744944572</v>
+        <v>0.004336177837103605</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.01057214755564928</v>
+        <v>0.002113055204972625</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.02957068756222725</v>
+        <v>0.004875534679740667</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1572312563657761</v>
+        <v>0.004729604348540306</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.01491923350840807</v>
+        <v>0.003474499564617872</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02185851521790028</v>
+        <v>0.0006241935188882053</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.01346388831734657</v>
+        <v>0.002201734576374292</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.09965522587299347</v>
+        <v>0.002404890023171902</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4966478645801544</v>
+        <v>0.01763303205370903</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09884227067232132</v>
+        <v>0.002583219902589917</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.06219321489334106</v>
+        <v>0.01329988613724709</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01412762887775898</v>
+        <v>0.01004269998520613</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.009018978103995323</v>
+        <v>0.01362417731434107</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01252287626266479</v>
+        <v>0.001531172078102827</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.00100617075804621</v>
+        <v>0.003955343272536993</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0835755467414856</v>
+        <v>0.003225925844162703</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1143604591488838</v>
+        <v>0.005529460497200489</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3993968963623047</v>
+        <v>0.003088456811383367</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1740088611841202</v>
+        <v>0.008161862380802631</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0898314043879509</v>
+        <v>0.000942752230912447</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01458471454679966</v>
+        <v>0.003855978604406118</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.07027231901884079</v>
+        <v>0.001601902302354574</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02632288634777069</v>
+        <v>0.002452116459608078</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.02731381729245186</v>
+        <v>0.0001634034852031618</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.04071315377950668</v>
+        <v>9.733368642628193e-05</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.197525754570961</v>
+        <v>0.0005014949711039662</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.04400431737303734</v>
+        <v>0.005060518160462379</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01635915413498878</v>
+        <v>0.0001751523814164102</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.09288206696510315</v>
+        <v>0.00328032486140728</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1459745317697525</v>
+        <v>0.001569776562973857</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.03976760059595108</v>
+        <v>0.003629958722740412</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01822300255298615</v>
+        <v>0.002172695240005851</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.006447356194257736</v>
+        <v>0.003193092066794634</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.07719866931438446</v>
+        <v>0.001994578633457422</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.103263184428215</v>
+        <v>0.001369120669551194</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2713220119476318</v>
+        <v>0.008334807120263577</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.09687738865613937</v>
+        <v>0.002823194954544306</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01353103294968605</v>
+        <v>0.00483525637537241</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1516687273979187</v>
+        <v>0.003815462114289403</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.06598207354545593</v>
+        <v>0.009970488026738167</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.008590969257056713</v>
+        <v>0.0003239806683268398</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002011826261878014</v>
+        <v>0.001044524949975312</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05585591495037079</v>
+        <v>0.001291123917326331</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.002755245892331004</v>
+        <v>0.001716725411824882</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1381942331790924</v>
+        <v>0.01104644499719143</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0275614857673645</v>
+        <v>0.002086613792926073</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.04353047162294388</v>
+        <v>0.004633932840079069</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01053779106587172</v>
+        <v>0.0008055671351030469</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0502944104373455</v>
+        <v>0.003551086410880089</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001118810381740332</v>
+        <v>0.0009818836115300655</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.01138927694410086</v>
+        <v>0.002772682812064886</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.03455745428800583</v>
+        <v>0.001193435629829764</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1275869905948639</v>
+        <v>0.002341837855055928</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1364355087280273</v>
+        <v>0.001991965109482408</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.01548353582620621</v>
+        <v>0.006480783224105835</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02656619064509869</v>
+        <v>0.005421418696641922</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1159571781754494</v>
+        <v>0.0102336872369051</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.2628195285797119</v>
+        <v>0.0005145264440216124</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0195516049861908</v>
+        <v>0.0005084178410470486</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.06488757580518723</v>
+        <v>0.006545610260218382</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.04382484406232834</v>
+        <v>0.002770961727946997</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.006801940500736237</v>
+        <v>0.002931874245405197</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1596142202615738</v>
+        <v>0.01044141501188278</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01376668177545071</v>
+        <v>0.002877924824133515</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04174790531396866</v>
+        <v>0.004080339334905148</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01864457875490189</v>
+        <v>0.001483769970946014</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.04485296830534935</v>
+        <v>0.004689247813075781</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0007541915401816368</v>
+        <v>0.00105024769436568</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.02037892304360867</v>
+        <v>0.002395516727119684</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.03407981619238853</v>
+        <v>0.0003589752595871687</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.04195284098386765</v>
+        <v>0.003843649756163359</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.3977992832660675</v>
+        <v>0.008514237590134144</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.05798419937491417</v>
+        <v>0.0001310133375227451</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.06362742930650711</v>
+        <v>0.002349474700167775</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.007307922467589378</v>
+        <v>0.0008784282254055142</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.1133002936840057</v>
+        <v>0.008927575312554836</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.01500826701521873</v>
+        <v>0.001648463658057153</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.005155771970748901</v>
+        <v>0.007357511669397354</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.01371457427740097</v>
+        <v>0.0003836494288407266</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.02095198631286621</v>
+        <v>0.0009251813171431422</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.1919300407171249</v>
+        <v>0.0008925338042899966</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.1013876050710678</v>
+        <v>0.003424209309741855</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.006616382859647274</v>
+        <v>0.003066931385546923</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1242272034287453</v>
+        <v>0.005341678392142057</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.05713064968585968</v>
+        <v>0.002824355848133564</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.03348257392644882</v>
+        <v>0.0004818896995857358</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.003082339651882648</v>
+        <v>0.005772901233285666</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0745820477604866</v>
+        <v>0.005487245973199606</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.01577960513532162</v>
+        <v>0.0007554237963631749</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1656041443347931</v>
+        <v>0.0009587461827322841</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.08513996005058289</v>
+        <v>0.006667122710496187</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.1268864125013351</v>
+        <v>0.00112128141336143</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.05547204613685608</v>
+        <v>0.003583336481824517</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.1476258635520935</v>
+        <v>0.006135135423392057</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.005798493046313524</v>
+        <v>0.002151068765670061</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.006930678617209196</v>
+        <v>0.008599030785262585</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.01764965802431107</v>
+        <v>0.006907242350280285</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.02585921436548233</v>
+        <v>0.002116364659741521</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.08061569184064865</v>
+        <v>0.01280687004327774</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.02218782901763916</v>
+        <v>0.002240996574983001</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.03379250317811966</v>
+        <v>0.00454500038176775</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.160169243812561</v>
+        <v>0.001133461715653539</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.03364111483097076</v>
+        <v>0.003385325660929084</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0109344944357872</v>
+        <v>0.000813155435025692</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.01281630154699087</v>
+        <v>0.001314365305006504</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.04037199169397354</v>
+        <v>0.0008433652110397816</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.01735377684235573</v>
+        <v>0.004102268256247044</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.1114202290773392</v>
+        <v>0.006382917053997517</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.1242152974009514</v>
+        <v>0.0005422233371064067</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03191719204187393</v>
+        <v>0.001336194109171629</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.193370059132576</v>
+        <v>0.001760528888553381</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.04872356355190277</v>
+        <v>0.001554301241412759</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.004421145189553499</v>
+        <v>0.0002445275895297527</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0765877440571785</v>
+        <v>0.002379373414441943</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.002622826024889946</v>
+        <v>0.0004995357012376189</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.01421457622200251</v>
+        <v>0.0017158726695925</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.1765632629394531</v>
+        <v>0.01180338207632303</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.01564550213515759</v>
+        <v>0.002237712033092976</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.02338788472115993</v>
+        <v>0.005293085239827633</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02680223807692528</v>
+        <v>0.0003462186141405255</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.01580226980149746</v>
+        <v>0.004298074170947075</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.009251443669199944</v>
+        <v>0.001190470531582832</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0003491742536425591</v>
+        <v>0.003039975417777896</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0436842106282711</v>
+        <v>0.0004356925783213228</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01827342435717583</v>
+        <v>0.0001743681932566687</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0766715332865715</v>
+        <v>0.009223779663443565</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.06951240450143814</v>
+        <v>0.002925219014286995</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.02981423027813435</v>
+        <v>0.001909887418150902</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.177396684885025</v>
+        <v>0.002392129274085164</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.06578309834003448</v>
+        <v>0.004383048042654991</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0120643638074398</v>
+        <v>5.367497215047479e-05</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.09118909388780594</v>
+        <v>0.005568981170654297</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0136202136054635</v>
+        <v>0.001004982274025679</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.1003864482045174</v>
+        <v>0.01145159173756838</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.04584871977567673</v>
+        <v>0.001334737171418965</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.02905763499438763</v>
+        <v>0.009825937449932098</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01688972301781178</v>
+        <v>0.001394265331327915</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.06015068292617798</v>
+        <v>0.01005532220005989</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.1337984949350357</v>
+        <v>0.003582702251151204</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.02922904677689075</v>
+        <v>0.002254639752209187</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0259045884013176</v>
+        <v>0.003811957081779838</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.003751758486032486</v>
+        <v>0.004844590090215206</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.05105327442288399</v>
+        <v>0.0005262652412056923</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.1214151233434677</v>
+        <v>0.003068357473239303</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.06663010269403458</v>
+        <v>0.003458831459283829</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02881369739770889</v>
+        <v>0.0003287822473794222</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.05440584942698479</v>
+        <v>0.000378312193788588</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.05354862660169601</v>
+        <v>0.00436454126611352</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.1094206422567368</v>
+        <v>0.002796050161123276</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.05971003696322441</v>
+        <v>0.001376653788611293</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0019337497651577</v>
+        <v>0.0003372917708475143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03685485571622849</v>
+        <v>0.1162147223949432</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02470461279153824</v>
+        <v>0.1310250908136368</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01024872623383999</v>
+        <v>0.116779737174511</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09109843522310257</v>
+        <v>0.02458358928561211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01926355808973312</v>
+        <v>0.1244092136621475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1275997906923294</v>
+        <v>0.3472833037376404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02634694054722786</v>
+        <v>0.04674575477838516</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04924162104725838</v>
+        <v>0.2320433408021927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01804420910775661</v>
+        <v>0.2665574550628662</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07179398834705353</v>
+        <v>0.04073185473680496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01959886401891708</v>
+        <v>0.1785682737827301</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02835535258054733</v>
+        <v>0.2742219567298889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004431212320923805</v>
+        <v>0.008378054946660995</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05985169112682343</v>
+        <v>0.07635510712862015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1148441955447197</v>
+        <v>0.4369746446609497</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01728763990104198</v>
+        <v>0.004985928535461426</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07497689872980118</v>
+        <v>0.3071204721927643</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03531517833471298</v>
+        <v>0.2789636552333832</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006530894432216883</v>
+        <v>0.04313172027468681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008213324472308159</v>
+        <v>0.107908695936203</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02466225624084473</v>
+        <v>0.03186515718698502</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02823113463819027</v>
+        <v>0.06597842276096344</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005938512273132801</v>
+        <v>0.1039064303040504</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0275544673204422</v>
+        <v>0.1109483018517494</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009870491921901703</v>
+        <v>0.01186585426330566</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005520771723240614</v>
+        <v>0.08028492331504822</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008094229269772768</v>
+        <v>0.01515994127839804</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04716498032212257</v>
+        <v>0.1801904588937759</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01238062232732773</v>
+        <v>0.3252678513526917</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02357550896704197</v>
+        <v>0.004021527245640755</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01228594500571489</v>
+        <v>0.05433101952075958</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.009018199518322945</v>
+        <v>0.1755393892526627</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.04261865839362144</v>
+        <v>0.07750885188579559</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0167124941945076</v>
+        <v>0.1155745163559914</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.009829333052039146</v>
+        <v>0.09626205265522003</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01449881307780743</v>
+        <v>0.04174216091632843</v>
       </c>
       <c r="AK3" t="n">
-        <v>7.945368997752666e-05</v>
+        <v>0.02648162469267845</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01715145446360111</v>
+        <v>0.03783955052495003</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01958114840090275</v>
+        <v>0.1121902465820312</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.00365865882486105</v>
+        <v>0.01820215582847595</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0001027436228469014</v>
+        <v>0.01587115228176117</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.01630501635372639</v>
+        <v>0.01386533491313457</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001403730013407767</v>
+        <v>0.03887739777565002</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01306547690182924</v>
+        <v>0.01406220905482769</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.000642963859718293</v>
+        <v>0.06895991414785385</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.01821784302592278</v>
+        <v>0.0577680878341198</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.008267647586762905</v>
+        <v>0.2402008026838303</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.04971189796924591</v>
+        <v>0.1120878234505653</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.003273816779255867</v>
+        <v>0.01206992752850056</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.02273261919617653</v>
+        <v>0.02091266214847565</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.03329089283943176</v>
+        <v>0.1053627580404282</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01864758133888245</v>
+        <v>0.01648136787116528</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.02439629286527634</v>
+        <v>0.1536963433027267</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001540901605039835</v>
+        <v>0.1448930650949478</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.01566695049405098</v>
+        <v>0.2420496642589569</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01646184548735619</v>
+        <v>0.08989622443914413</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.03560339659452438</v>
+        <v>0.007745455950498581</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.06294558197259903</v>
+        <v>0.0133715495467186</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.002736668568104506</v>
+        <v>0.07444701343774796</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.07414332777261734</v>
+        <v>0.04307994991540909</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.008930087089538574</v>
+        <v>0.03231129050254822</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01524584367871284</v>
+        <v>0.0693504586815834</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01931082829833031</v>
+        <v>0.003344276919960976</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02642586641013622</v>
+        <v>0.04785637184977531</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.08755698055028915</v>
+        <v>0.04335378855466843</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.04716327786445618</v>
+        <v>0.1082126349210739</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.007131333462893963</v>
+        <v>0.03850911557674408</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01572532020509243</v>
+        <v>0.1100804284214973</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01126577146351337</v>
+        <v>0.05070549622178078</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.002254391089081764</v>
+        <v>0.03266724944114685</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01607017032802105</v>
+        <v>0.1025626510381699</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.013756955973804</v>
+        <v>0.1090819910168648</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001137122046202421</v>
+        <v>0.113274097442627</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.006343337241560221</v>
+        <v>0.1038638055324554</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.03114073909819126</v>
+        <v>0.004915995523333549</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.005544015672057867</v>
+        <v>0.02406505309045315</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.03006897121667862</v>
+        <v>0.02581839263439178</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.02976952865719795</v>
+        <v>0.007710214238613844</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.008073435164988041</v>
+        <v>0.0164553914219141</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.007415478117763996</v>
+        <v>0.1562099009752274</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.004742187447845936</v>
+        <v>0.1067050024867058</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01735975965857506</v>
+        <v>0.05471017211675644</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.01848595589399338</v>
+        <v>0.06223643943667412</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.002106263302266598</v>
+        <v>0.0954291969537735</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.002842470072209835</v>
+        <v>0.02415150031447411</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.003722038120031357</v>
+        <v>0.007434053346514702</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.02277845703065395</v>
+        <v>0.04004493728280067</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.000207425415283069</v>
+        <v>0.01518527790904045</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0006129338871687651</v>
+        <v>0.02472815290093422</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.001448201132006943</v>
+        <v>0.03963878750801086</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.002199702896177769</v>
+        <v>0.09782335162162781</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.008933259174227715</v>
+        <v>0.003132473677396774</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.01240922417491674</v>
+        <v>0.1108677685260773</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.001922654919326305</v>
+        <v>0.06222552806138992</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.02110286056995392</v>
+        <v>0.2643141150474548</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01238714158535004</v>
+        <v>0.2869905531406403</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.01463486813008785</v>
+        <v>0.03458831831812859</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.007377478294074535</v>
+        <v>0.07831744104623795</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.01104614231735468</v>
+        <v>0.02272982895374298</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02257421426475048</v>
+        <v>0.07194182276725769</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03050495497882366</v>
+        <v>0.04824970662593842</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.005892855115234852</v>
+        <v>0.1027379482984543</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.003481687512248755</v>
+        <v>0.01240843441337347</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005362304858863354</v>
+        <v>0.002254709601402283</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01472043246030807</v>
+        <v>0.04443522915244102</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0009569023968651891</v>
+        <v>0.01647010259330273</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.006642175372689962</v>
+        <v>0.01649201475083828</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.004352252930402756</v>
+        <v>0.05363660678267479</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0325448252260685</v>
+        <v>0.1652754545211792</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.03781479969620705</v>
+        <v>0.4045400023460388</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.01224522199481726</v>
+        <v>0.0002235099673271179</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1229850202798843</v>
+        <v>0.238666906952858</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0006240414222702384</v>
+        <v>0.1144865453243256</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.03359176963567734</v>
+        <v>0.182345524430275</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.03686900436878204</v>
+        <v>0.03945926949381828</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.04753459617495537</v>
+        <v>0.002517155837267637</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001097467611543834</v>
+        <v>0.06232584267854691</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01338199898600578</v>
+        <v>0.1230926290154457</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.03141684085130692</v>
+        <v>0.0331106148660183</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01953667402267456</v>
+        <v>0.1137734577059746</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.002336664590984583</v>
+        <v>0.0770658552646637</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.03798720985651016</v>
+        <v>0.04194118827581406</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.003521567676216364</v>
+        <v>0.05987825617194176</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.006686968728899956</v>
+        <v>0.03308200463652611</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01600207388401031</v>
+        <v>0.07909879833459854</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.006453008390963078</v>
+        <v>0.03704581037163734</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03530421108007431</v>
+        <v>0.03530361503362656</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0410025343298912</v>
+        <v>0.02533556893467903</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.03271763026714325</v>
+        <v>0.1838018894195557</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.02045621909201145</v>
+        <v>0.0223793089389801</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.003557125106453896</v>
+        <v>0.1793810278177261</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03323444351553917</v>
+        <v>0.01795076951384544</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01516809314489365</v>
+        <v>0.02201969176530838</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.03708909079432487</v>
+        <v>0.04918185248970985</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0005153696401976049</v>
+        <v>0.1051038503646851</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0241282545030117</v>
+        <v>0.09944457560777664</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.002275259234011173</v>
+        <v>0.08889094740152359</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0007415935397148132</v>
+        <v>0.06342026591300964</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.006847026757895947</v>
+        <v>0.01982628740370274</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.008332686498761177</v>
+        <v>0.1057027950882912</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0298441406339407</v>
+        <v>0.01062692515552044</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.007994402199983597</v>
+        <v>0.03252052515745163</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.006187501363456249</v>
+        <v>0.04279705509543419</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.009078081697225571</v>
+        <v>0.06386061757802963</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.03424417600035667</v>
+        <v>0.03141504898667336</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.006448361556977034</v>
+        <v>0.0671088695526123</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.02789045125246048</v>
+        <v>0.0829584002494812</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.002204794669523835</v>
+        <v>0.1259112358093262</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.05477941036224365</v>
+        <v>0.1475869566202164</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.007858213037252426</v>
+        <v>0.01884781569242477</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0007078759372234344</v>
+        <v>0.09118855744600296</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.003138372208923101</v>
+        <v>0.01461057923734188</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.008915085345506668</v>
+        <v>0.07950408756732941</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02686707675457001</v>
+        <v>0.06665199995040894</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.02425207197666168</v>
+        <v>0.05859145149588585</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.007535876706242561</v>
+        <v>0.06711950898170471</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.006936295889317989</v>
+        <v>0.002930800430476665</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01484729256480932</v>
+        <v>0.00950985960662365</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.02255679108202457</v>
+        <v>0.04666984081268311</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.002344625070691109</v>
+        <v>0.02581718564033508</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.002514974446967244</v>
+        <v>0.01717675291001797</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0008951282361522317</v>
+        <v>0.04258580133318901</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.001350286300294101</v>
+        <v>0.1408774703741074</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01058252714574337</v>
+        <v>0.0553765557706356</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03054300136864185</v>
+        <v>0.003442294895648956</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.03406766057014465</v>
+        <v>0.04832522943615913</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.03784789517521858</v>
+        <v>0.09464078396558762</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.002580411033704877</v>
+        <v>0.02121672779321671</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.004487533122301102</v>
+        <v>0.03775232657790184</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.008864222094416618</v>
+        <v>0.05087584257125854</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.01726757921278477</v>
+        <v>0.1327077448368073</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.001817747950553894</v>
+        <v>0.2506747841835022</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.05081211403012276</v>
+        <v>0.08631617575883865</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.03391801193356514</v>
+        <v>0.2000109255313873</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.01308494620025158</v>
+        <v>0.2046561539173126</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.02901662327349186</v>
+        <v>0.02910059876739979</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.02467332221567631</v>
+        <v>0.1763715296983719</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.02512836456298828</v>
+        <v>0.293036162853241</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0335695818066597</v>
+        <v>0.3093833327293396</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.01661617681384087</v>
+        <v>0.1815757006406784</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.01125196367502213</v>
+        <v>0.1673917174339294</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.00741938641294837</v>
+        <v>0.1768537312746048</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0309525765478611</v>
+        <v>0.2815671861171722</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03244265168905258</v>
+        <v>0.0497511588037014</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.02037220820784569</v>
+        <v>0.04744779318571091</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.01542175374925137</v>
+        <v>0.03253242373466492</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.004433112218976021</v>
+        <v>0.01014854479581118</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0360233411192894</v>
+        <v>0.07468627393245697</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.003968114499002695</v>
+        <v>0.009671407751739025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.329199585597962e-05</v>
+        <v>5.468566087074578e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0002569516655057669</v>
+        <v>0.0004384873318485916</v>
       </c>
       <c r="C4" t="n">
-        <v>4.737650306196883e-05</v>
+        <v>0.0001546614657854661</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005630847881548107</v>
+        <v>0.0002460961695760489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001282968005398288</v>
+        <v>9.661597141530365e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>8.217876893468201e-05</v>
+        <v>0.0003353702486492693</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55075395014137e-06</v>
+        <v>0.000116628194518853</v>
       </c>
       <c r="H4" t="n">
-        <v>5.423967377282679e-05</v>
+        <v>9.399665941600688e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.719210796291009e-05</v>
+        <v>0.0001447106769774109</v>
       </c>
       <c r="J4" t="n">
-        <v>9.937075810739771e-05</v>
+        <v>6.920428859302774e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002393330651102588</v>
+        <v>0.0004340627929195762</v>
       </c>
       <c r="L4" t="n">
-        <v>1.535878982394934e-05</v>
+        <v>0.0002715566079132259</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0005578074487857521</v>
+        <v>0.0005434395861811936</v>
       </c>
       <c r="N4" t="n">
-        <v>2.153608875232749e-05</v>
+        <v>0.0001086023476091214</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002765338867902756</v>
+        <v>0.0003517124569043517</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001041107680066489</v>
+        <v>5.337399852578528e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001485130778746679</v>
+        <v>0.0001247022009920329</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002029594907071441</v>
+        <v>0.0001107931166188791</v>
       </c>
       <c r="S4" t="n">
-        <v>9.346582373837009e-05</v>
+        <v>1.413071004208177e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001239540288224816</v>
+        <v>1.594032437424175e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.153190118609928e-05</v>
+        <v>2.18050045077689e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.581847755005583e-06</v>
+        <v>0.0001057714980561286</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001196362427435815</v>
+        <v>8.730293484404683e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001166920701507479</v>
+        <v>6.395898526534438e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.854851118172519e-05</v>
+        <v>2.048577516688965e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.047275797347538e-05</v>
+        <v>5.463238994707353e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.10506798591814e-05</v>
+        <v>1.795151183614507e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.947985770646483e-05</v>
+        <v>0.0001261101278942078</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0001093300088541582</v>
+        <v>0.0001474734744988382</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.238409433630295e-05</v>
+        <v>6.687361747026443e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.226732072420418e-05</v>
+        <v>4.940529834129848e-06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0002327671536477283</v>
+        <v>1.937627348524984e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.732858047238551e-05</v>
+        <v>6.489321094704792e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.035191548406146e-05</v>
+        <v>1.74616179720033e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.533321043709293e-05</v>
+        <v>0.0001157321312348358</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.077906386461109e-05</v>
+        <v>2.113107257173397e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>8.502528362441808e-05</v>
+        <v>4.111145244678482e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.000179216978722252</v>
+        <v>5.647065700031817e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.285264715988887e-05</v>
+        <v>2.245074938400649e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.731563240056857e-05</v>
+        <v>1.1239410014241e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.080920007254463e-06</v>
+        <v>8.372937008971348e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.299463060102426e-05</v>
+        <v>8.64574103616178e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.212578328908421e-05</v>
+        <v>8.96341516636312e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.294587804703042e-05</v>
+        <v>6.010559445712715e-07</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.841934060095809e-05</v>
+        <v>2.497438435966615e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.149056520778686e-05</v>
+        <v>5.843834151164629e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.245855522342026e-05</v>
+        <v>0.0002292033168487251</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.627381607249845e-05</v>
+        <v>0.0001254390808753669</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.000256576924584806</v>
+        <v>5.384738869906869e-06</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.830860754940659e-05</v>
+        <v>0.0003728076699189842</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.14641726820264e-05</v>
+        <v>0.0002770932333078235</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0001044357268256135</v>
+        <v>2.027399750659242e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.337710611755028e-06</v>
+        <v>0.0001345743221463636</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.325210178038105e-06</v>
+        <v>1.767764297255781e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.034146175195929e-05</v>
+        <v>4.728169733425602e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0001062842784449458</v>
+        <v>1.873397195595317e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.530576603021473e-05</v>
+        <v>0.0001063252711901441</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0002389581059105694</v>
+        <v>0.0001638914400245994</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.847480547847226e-05</v>
+        <v>0.0003790607152041048</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.990826659603044e-05</v>
+        <v>1.851933120633475e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.631660390761681e-05</v>
+        <v>5.998818960506469e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6.520677743537817e-06</v>
+        <v>9.217744263878558e-06</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.110812627302948e-05</v>
+        <v>9.022129233926535e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001720170403132215</v>
+        <v>5.404122930485755e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0001575744390720502</v>
+        <v>3.869283318636008e-06</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.679508568486199e-05</v>
+        <v>6.938567821634933e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.539311364875175e-05</v>
+        <v>0.0001634197833482176</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.031400855339598e-06</v>
+        <v>0.0002617482678033412</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.904872235376388e-05</v>
+        <v>7.309525972232223e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.617004454601556e-05</v>
+        <v>0.0001522863021818921</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.962828825227916e-06</v>
+        <v>6.668730202363804e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.199710408807732e-05</v>
+        <v>5.638244147121441e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0001190316543215886</v>
+        <v>2.057057827187236e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.565296932123601e-05</v>
+        <v>9.515923011349514e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.129606243921444e-05</v>
+        <v>1.220379272126593e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>7.943659147713333e-05</v>
+        <v>8.209409133996814e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0001143267072620802</v>
+        <v>0.0001003866345854476</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.487087037181482e-06</v>
+        <v>0.0001284074824070558</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.155687828548253e-05</v>
+        <v>0.0001092902821255848</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.17491649184376e-05</v>
+        <v>7.851178816054016e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>9.308024164056405e-05</v>
+        <v>7.56838999222964e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>7.886737876106054e-05</v>
+        <v>2.683673665160313e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>2.090905218210537e-05</v>
+        <v>0.0001517242490081117</v>
       </c>
       <c r="CF4" t="n">
-        <v>4.553681264951592e-06</v>
+        <v>3.631981235230342e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0001320441369898617</v>
+        <v>0.0001014763838611543</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.006936069345102e-05</v>
+        <v>6.823047442594543e-07</v>
       </c>
       <c r="CI4" t="n">
-        <v>3.383890725672245e-05</v>
+        <v>7.706247561145574e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.842661317321472e-05</v>
+        <v>4.798055306309834e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>3.472460593911819e-05</v>
+        <v>5.314930967870168e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.35696934396401e-05</v>
+        <v>4.032057404401712e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.431307777645998e-05</v>
+        <v>6.887471499794628e-06</v>
       </c>
       <c r="CN4" t="n">
-        <v>8.167564374161884e-06</v>
+        <v>8.803208766039461e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>9.502799002802931e-06</v>
+        <v>0.0001270760694751516</v>
       </c>
       <c r="CP4" t="n">
-        <v>9.914411930367351e-05</v>
+        <v>1.13723781396402e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>5.562284059124067e-05</v>
+        <v>6.380800914485008e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>4.462094511836767e-05</v>
+        <v>1.235870604432421e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0001473455922678113</v>
+        <v>0.0001100898880395107</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0001854242873378098</v>
+        <v>1.269708809559233e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>8.35526006994769e-05</v>
+        <v>6.344795838231221e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>9.257669444195926e-05</v>
+        <v>8.995923053589649e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>3.117957021459006e-05</v>
+        <v>0.0001204559885081835</v>
       </c>
       <c r="CX4" t="n">
-        <v>2.712680543481838e-05</v>
+        <v>5.423642869573087e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0001093976898118854</v>
+        <v>9.49846362345852e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.402815491426736e-05</v>
+        <v>1.868652907432988e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>5.769116614828818e-05</v>
+        <v>0.0001143394329119474</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.712505713338032e-05</v>
+        <v>7.357259164564312e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.687186861294322e-05</v>
+        <v>6.019310239935294e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.030357038369402e-05</v>
+        <v>4.200950934318826e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.188031092169695e-05</v>
+        <v>4.621469634003006e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.000257141946349293</v>
+        <v>3.467901115072891e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0001248399348696694</v>
+        <v>0.0002957393880933523</v>
       </c>
       <c r="DH4" t="n">
-        <v>3.549231769284233e-05</v>
+        <v>5.836768195877085e-06</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001499464560765773</v>
+        <v>6.297901563812047e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0001847626554081216</v>
+        <v>0.0001988833246286958</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.000166469078976661</v>
+        <v>0.000175279623363167</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.535082578309812e-05</v>
+        <v>0.0001158041777671315</v>
       </c>
       <c r="DM4" t="n">
-        <v>9.685772238299251e-05</v>
+        <v>1.71757310454268e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>5.84312692808453e-05</v>
+        <v>1.206022989208577e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.452587978041265e-05</v>
+        <v>0.0001145845162682235</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.904332935344428e-05</v>
+        <v>5.036599395680241e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0001447221293346956</v>
+        <v>2.262164525745902e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.574902802938595e-05</v>
+        <v>5.71720829611877e-06</v>
       </c>
       <c r="DS4" t="n">
-        <v>3.751788244699128e-05</v>
+        <v>0.0001205804219353013</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.029114148172084e-05</v>
+        <v>3.571494380594231e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.179616421926767e-05</v>
+        <v>0.0001608734310138971</v>
       </c>
       <c r="DV4" t="n">
-        <v>4.657117824535817e-05</v>
+        <v>5.876164141227491e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0001422932255081832</v>
+        <v>1.928546407725662e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>6.778570241294801e-05</v>
+        <v>0.0001592756161699072</v>
       </c>
       <c r="DY4" t="n">
-        <v>4.314500984037295e-05</v>
+        <v>3.594194276956841e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.731009878218174e-05</v>
+        <v>0.00011925317812711</v>
       </c>
       <c r="EA4" t="n">
-        <v>8.510328189004213e-05</v>
+        <v>0.0001103087051887996</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.00011049336171709</v>
+        <v>3.648742131190374e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>8.336777682416141e-05</v>
+        <v>0.0002193488471675664</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.000121275894343853</v>
+        <v>6.308757292572409e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.962313399417326e-05</v>
+        <v>0.0001280586584471166</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.551175773784053e-05</v>
+        <v>1.826473817345686e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>9.396186214871705e-06</v>
+        <v>2.743063305388205e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.305623663938604e-05</v>
+        <v>1.237543983734213e-06</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.000193567801034078</v>
+        <v>8.093052019830793e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>5.471289114211686e-05</v>
+        <v>5.443853297038004e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>3.39118037118169e-06</v>
+        <v>2.866567228920758e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>8.801362127996981e-06</v>
+        <v>8.353063458343968e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>8.123567386064678e-05</v>
+        <v>4.259410707163624e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>3.852153895422816e-05</v>
+        <v>0.0001499097124906257</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0001562455727253109</v>
+        <v>4.718759555544239e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>5.315105227055028e-07</v>
+        <v>0.0001700336579233408</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0001095799234462902</v>
+        <v>2.647616565809585e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0001113584294216707</v>
+        <v>2.225928801635746e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>3.25110318044608e-06</v>
+        <v>7.249436748679727e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001527034910395741</v>
+        <v>0.0001239174162037671</v>
       </c>
       <c r="EU4" t="n">
-        <v>9.814848453970626e-06</v>
+        <v>6.355546793201938e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>7.352034299401566e-05</v>
+        <v>3.849017230095342e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>7.594278577016667e-05</v>
+        <v>2.74279391305754e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001110057273763232</v>
+        <v>5.495182631420903e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>3.069454032811336e-05</v>
+        <v>0.0001393444545101374</v>
       </c>
       <c r="EZ4" t="n">
-        <v>3.048913276870735e-05</v>
+        <v>1.636487650102936e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.000127369596157223</v>
+        <v>7.496467878809199e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>5.412449536379427e-05</v>
+        <v>9.62401827564463e-07</v>
       </c>
       <c r="FC4" t="n">
-        <v>3.481519524939358e-05</v>
+        <v>8.274593710666522e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.390575900790282e-05</v>
+        <v>5.794220487587154e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>4.852884558204096e-06</v>
+        <v>6.916772690601647e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>5.069129110779613e-05</v>
+        <v>4.621426342055202e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>7.937367627164349e-05</v>
+        <v>0.00013443072384689</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0001615721703274176</v>
+        <v>7.815119170118123e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>1.57706017489545e-06</v>
+        <v>6.95539201842621e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>6.499596202047542e-05</v>
+        <v>2.213135303463787e-06</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0001012923894450068</v>
+        <v>1.806862928788178e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>1.544782026030589e-05</v>
+        <v>2.783306990750134e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0001108515280066058</v>
+        <v>0.0001823500351747498</v>
       </c>
       <c r="FN4" t="n">
-        <v>4.394833740661852e-05</v>
+        <v>4.715419709100388e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.415998889977345e-06</v>
+        <v>0.0001693027443252504</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0001735060068313032</v>
+        <v>0.0001123878755606711</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0001355969288852066</v>
+        <v>0.0002487918827682734</v>
       </c>
       <c r="FR4" t="n">
-        <v>1.176340447273105e-07</v>
+        <v>5.329323903424665e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>3.378420660737902e-05</v>
+        <v>0.0001051192230079323</v>
       </c>
       <c r="FT4" t="n">
-        <v>2.033854798355605e-05</v>
+        <v>7.274721428984776e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>9.101905743591487e-05</v>
+        <v>3.75861191059812e-06</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0003358503454364836</v>
+        <v>1.31838987726951e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0001858936448115855</v>
+        <v>7.858712342567742e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.019426003447734e-05</v>
+        <v>3.087469303864054e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0002079916594084352</v>
+        <v>5.974568921374157e-06</v>
       </c>
       <c r="FZ4" t="n">
-        <v>4.689106208388694e-05</v>
+        <v>2.866425893444102e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001761180610628799</v>
+        <v>0.0001477962941862643</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.82741675619036e-05</v>
+        <v>2.950698217318859e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0001796817232389003</v>
+        <v>6.017313717165962e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0001228914625244215</v>
+        <v>1.879064257082064e-06</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0001510574365966022</v>
+        <v>4.868884934694506e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0001306338381255046</v>
+        <v>0.0001295847032452002</v>
       </c>
       <c r="GG4" t="n">
-        <v>8.361434447579086e-05</v>
+        <v>1.811063157219905e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>0.04245322570204735</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.02802671119570732</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.03609476983547211</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.01019623316824436</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.05149707943201065</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0425381064414978</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.05458351597189903</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.03179426491260529</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.03280322253704071</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.03741221129894257</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.05721734464168549</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.03339723125100136</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.01332645025104284</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.0354984886944294</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.03984511271119118</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.06612919270992279</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.02408183738589287</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.02339114435017109</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.003988672513514757</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.007300999015569687</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.02097042463719845</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.03362702578306198</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.005392872728407383</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.02322762086987495</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.0006212638691067696</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.02694079093635082</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.01445483602583408</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.01246538292616606</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.03253505378961563</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.01200276706367731</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.02921325527131557</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.02109718322753906</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.01022324338555336</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.02129586413502693</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>0.02059069275856018</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.006198702845722437</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.01895025931298733</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.03330449014902115</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.007425455376505852</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>0.01401438377797604</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>0.01966026425361633</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.02471417933702469</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.01254902593791485</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.0002947915345430374</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>0.00471425848081708</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>0.01724428310990334</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.04487654939293861</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.04881252348423004</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.001501340884715319</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>0.0250707920640707</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>0.04681696370244026</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.008725257590413094</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>0.02809887006878853</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>0.03514378517866135</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>0.01267240662127733</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>0.02472605183720589</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>0.02861395664513111</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>0.00281674275174737</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>0.003254065290093422</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>0.04411400482058525</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>0.03810634091496468</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.03749086707830429</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.01854843832552433</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>0.007251457311213017</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>0.008997178636491299</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>0.003982812166213989</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.01010228786617517</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>0.005572267808020115</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>0.009879274293780327</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>0.0116980466991663</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>0.02188112214207649</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>0.001531875226646662</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>0.01316646859049797</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.04129423946142197</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>0.02346683293581009</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>0.03373229876160622</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>0.03085531108081341</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>0.03792544826865196</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>0.01563351415097713</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>0.03184081614017487</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>0.01524175330996513</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>0.007237665355205536</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>0.0126202255487442</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>0.01004632003605366</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.004324399400502443</v>
       </c>
       <c r="CH5" t="n">
-        <v>0</v>
+        <v>0.008756033144891262</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.01816669106483459</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>0.008362255990505219</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>0.01290751900523901</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>0.008152157068252563</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>0.001456424593925476</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>0.04027973860502243</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.005994468927383423</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.001281384378671646</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0</v>
+        <v>0.06139485538005829</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>0.07705296576023102</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>0.009163284674286842</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>0.01664193347096443</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>0.01485848985612392</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>0.00768998172134161</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>0.002014914294704795</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>0.00781742949038744</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>0.005884728860110044</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>0.004144636914134026</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>0.01345979142934084</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>0.006821371149271727</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>0.003109966404736042</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>0.001684898394159973</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.01061426661908627</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>0.0109716160222888</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>0.01088182255625725</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.01109757926315069</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>0.03575858846306801</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>0.02942264266312122</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>0.01277362369000912</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.007230164017528296</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>0.02826040983200073</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>0.01540948078036308</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>0.04116221144795418</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>0.03081061691045761</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.004994716495275497</v>
       </c>
       <c r="DR5" t="n">
-        <v>0</v>
+        <v>0.02347851172089577</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.02982727997004986</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>4.968233406543732e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>0.01869816333055496</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>0.03651228547096252</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.009427626617252827</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>0.0003410540521144867</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>0.02672410942614079</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>0.03196817636489868</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>0.07574382424354553</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>0.02758908644318581</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>0.008018545806407928</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>0.01455299742519855</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>0.01608389802277088</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>0.004542933311313391</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>0.001467394642531872</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>0.01429132185876369</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>0.007700373884290457</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>0.009337702766060829</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>0.004687506705522537</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>0.005471920128911734</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>0.005587946623563766</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>0.009865588508546352</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>0.006179120391607285</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>0.01389000751078129</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>0.01184136420488358</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>0.01296941749751568</v>
       </c>
       <c r="ES5" t="n">
-        <v>0</v>
+        <v>0.04939816519618034</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>0.007644698023796082</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>0.0255344994366169</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>0.01281719468533993</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>0.0002079568803310394</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>0.006193951703608036</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>0.009022489190101624</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>0.003814825788140297</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.001223142025992274</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>0.003237452358007431</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>0.007321438286453485</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>0.003817647695541382</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>0.01162339746952057</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>0.00366316270083189</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>0.01047659013420343</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>0.0007361620664596558</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>0.01116346195340157</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>0.01237132027745247</v>
       </c>
       <c r="FK5" t="n">
-        <v>0</v>
+        <v>0.07839721441268921</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>0.02250451408326626</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>0.001012896187603474</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>0.01402009092271328</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>0.03711661696434021</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>0.01042421720921993</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>0.05899173021316528</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>0.02962681092321873</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.03716934844851494</v>
       </c>
       <c r="FT5" t="n">
-        <v>0</v>
+        <v>0.01559016853570938</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>0.01721476204693317</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>0.000887683592736721</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>0.04700320586562157</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>0.02775208279490471</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>0.005673516541719437</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>0.008955839090049267</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>0.03641129285097122</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.03402528166770935</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>0.01816934533417225</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>0.008413953706622124</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>0.005080056842416525</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>0.001912862528115511</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>0.02394271641969681</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3.359332549734972e-05</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6.252003367990255e-05</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.443050223315367e-06</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.789836905023549e-06</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.293506102229003e-05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75696022779448e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.430013051314745e-06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.766158548998646e-06</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.992375347181223e-06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.494517684681341e-05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.057614857330918e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.831033841881435e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.107933439925546e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.637387478898745e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.305893031007145e-05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.886312865437503e-08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.546486580802593e-06</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.184925324399956e-05</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.379860340326559e-06</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.934101874212502e-06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7.149384146032389e-06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.439066393999383e-06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.409508331562392e-05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.704850082111079e-06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.215255547838751e-06</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.073776638804702e-05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.456567926856223e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.862074208882404e-06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.146695224946598e-06</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5.896447873965371e-06</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.443661105644424e-05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.303000292158686e-05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.352812084107427e-06</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>7.669204933336005e-06</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.704410715319682e-05</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>8.013024853426032e-06</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.265319588128477e-05</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>7.642294804099947e-06</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7.973794708959758e-06</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.576601789565757e-05</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.285298822040204e-06</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6.545595624629641e-06</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.055095344781876e-05</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.224732608941849e-06</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.067856141569791e-06</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.790662281564437e-05</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.646835805033334e-05</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.850292942952365e-09</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.376988727017306e-06</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.440567368466873e-05</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.271565088245552e-05</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.982857722599874e-06</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.351191692985594e-06</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.003734814730706e-05</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.058392717823153e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.212253482663073e-05</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.067479661287507e-05</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.219690031779464e-07</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.174066801468143e-05</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.730970876058564e-06</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>8.475837603327818e-06</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>7.673981599509716e-06</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.61895820585778e-06</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2.434536327200476e-06</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5.021142897021491e-06</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.324877416664094e-07</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.092828021384776e-06</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.239450284629129e-05</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>3.474038294370985e-06</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1.56806199811399e-05</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>3.395525709493086e-06</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1.00056649898761e-05</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>2.306047099409625e-05</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>2.752353975665756e-05</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>4.064107088197488e-06</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>5.084201802674215e-06</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>5.147179763298482e-06</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.429800613550469e-05</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>9.490714546700474e-06</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.401536787350778e-06</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3.195754516127636e-06</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>8.995626558316872e-06</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1.863719808170572e-05</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1.877738213806879e-06</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3.282673787907697e-06</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.585895233802148e-06</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>6.268930519581772e-06</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>4.769543465954484e-06</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>9.725715699460125e-07</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>3.24796110362513e-06</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>7.150040346459718e-06</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.346156725252513e-05</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.04061091406038e-05</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>5.514054919331102e-06</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1.123714446293889e-05</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.602720112714451e-05</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>2.638745627336903e-06</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>6.804102667956613e-07</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>5.681231868948089e-06</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>6.840620244474849e-06</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1.728752795315813e-05</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>2.899643277487485e-06</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.606134785310132e-06</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.777303168637445e-06</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>6.811632374592591e-06</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.068857500285958e-06</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>5.087286808702629e-06</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>2.361501174164005e-06</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>2.259203938592691e-06</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>6.805235898355022e-06</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>4.334062396083027e-06</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>6.916308848303743e-06</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>2.478051101206802e-05</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>5.6620774557814e-07</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>7.923383236629888e-06</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>6.363462489389349e-06</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>7.151598765631206e-06</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>1.352401227450173e-06</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.424511719960719e-05</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>7.484597517759539e-06</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>3.827699401881546e-06</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>6.763972123735584e-06</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>1.257735129911453e-05</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>2.204599695687648e-06</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>1.205039097840199e-05</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>9.967408914235421e-06</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>5.724558832298499e-06</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>9.8863974926644e-06</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>1.661856458667899e-06</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>7.962362360558473e-06</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>3.280639475633507e-06</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1.702027930150507e-06</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>8.407232598983683e-07</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>1.279379739571596e-05</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>4.602759872796014e-06</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>9.971356121241115e-06</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>1.278086301681469e-06</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>6.569704964931589e-06</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>1.557795030748821e-06</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>2.249860017400351e-06</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>3.828293301921804e-06</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>1.259181203749904e-07</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>2.26806037062488e-06</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>2.316208792763064e-06</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>1.032506679621292e-05</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>4.317860657465644e-06</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>3.777912752411794e-06</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>2.68221242549771e-06</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>1.383673952659592e-05</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>1.401582994731143e-05</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>4.043854005431058e-06</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>1.051828576237313e-06</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>1.048493777489057e-05</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>8.739169061300345e-06</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>2.00831018446479e-05</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>8.525372550138854e-07</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>2.118117890859139e-06</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>1.288207840843825e-06</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>4.98737199450261e-06</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>5.480832442117389e-06</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>2.286227527292795e-06</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>1.226787844643695e-07</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>5.885508471692447e-07</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>1.262344176211627e-05</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>8.948893992055673e-06</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>7.718900633335579e-06</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>1.285321786781424e-06</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>1.587216866028029e-05</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>3.497495526971761e-06</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>5.286334271659143e-06</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>9.138214409176726e-06</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>1.879849514807574e-05</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>2.313319237146061e-05</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>4.175164576736279e-06</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>1.80277584149735e-05</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>5.798471647722181e-06</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>1.238567529071588e-05</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>1.223527942784131e-05</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>1.115359191317111e-05</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>6.601056611543754e-06</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>9.968502126866952e-06</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>4.146625087741995e-07</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>7.695124622841831e-06</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>3.669562602226506e-06</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>6.20893524683197e-06</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>1.247873660759069e-05</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>1.15381235445966e-05</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>5.173317731532734e-06</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>1.37306415126659e-05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.0415605828166008</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.07893162220716476</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06663045287132263</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008738653734326363</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.06339198350906372</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1713807284832001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04540134221315384</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.114546611905098</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.03927093371748924</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02977829799056053</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.06634917855262756</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06895521283149719</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.02942368201911449</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1003366336226463</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1578365415334702</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.04067955166101456</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1567691117525101</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.08086317777633667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01302870735526085</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.02899906411767006</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01385332550853491</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.004916264675557613</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.02540656737983227</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.008049880154430866</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01499154884368181</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.201715975999832e-05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01072319783270359</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.02764819748699665</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.01460685953497887</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.004714265465736389</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.04662708938121796</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.07126869261264801</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.01049954257905483</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.01077525038272142</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.008193729445338249</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.01340372860431671</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.02401173487305641</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.04409192875027657</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.006264227908104658</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.02728045731782913</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.04277486354112625</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.05704788118600845</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.02453375421464443</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.01898512430489063</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.009041610173881054</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.02284079417586327</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.1783556044101715</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.01179002970457077</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.001050079241394997</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.01127062551677227</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.04472322762012482</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.03418740630149841</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.02155954763293266</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.04483157396316528</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.02667919173836708</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.1322399377822876</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.046098243445158</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.01273095700889826</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.1157066524028778</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.03599675744771957</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.005595680326223373</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0106918029487133</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.02048175036907196</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.01256570313125849</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.01530024874955416</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.06569378077983856</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.01323956809937954</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.01233758591115475</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.0351637527346611</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.01809527166187763</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.04439237341284752</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.02709008753299713</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.01648109033703804</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.08681459724903107</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0007697101682424545</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.01691203564405441</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0294724702835083</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.03928245976567268</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.02887479215860367</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.001321369083598256</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.01189792808145285</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.002338652731850743</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.02856558933854103</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.03708187118172646</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.007180089596658945</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.01649169996380806</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.03413192182779312</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.00672138761729002</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.02539977990090847</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.01597865112125874</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.008281639777123928</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.008799633011221886</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.03811775892972946</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.02911870367825031</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.0563238337635994</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.02413016930222511</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.008467314764857292</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.02638214267790318</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.008931639604270458</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.006108652334660292</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.02072509564459324</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.03396515548229218</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.001585243735462427</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.02685491740703583</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.04475059360265732</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.001571876462548971</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.02514543943107128</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.01847436092793941</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.04888880625367165</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.01537010259926319</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.0005925931036472321</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.03450086712837219</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.01857475563883781</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.01015210710465908</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.02161677181720734</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.02921432070434093</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.06961081922054291</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.001219736179336905</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.03590371459722519</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.02567249163985252</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.002767424564808607</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.01916099898517132</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.02672381699085236</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.02003793232142925</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.01063408143818378</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.02947784587740898</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.004384995438158512</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.03543850407004356</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.07155637443065643</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.02704870887100697</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.01245843525975943</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.007036586292088032</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.006388053297996521</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.03839792311191559</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.03932349383831024</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.00472208671271801</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.00325976824387908</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.013654425740242</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.01017771754413843</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.05593963712453842</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.01179883629083633</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.005613805260509253</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.03137392923235893</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.01556720957159996</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.01579142361879349</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.05301283299922943</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.00125849898904562</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.003073973581194878</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.007528211921453476</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.03788766264915466</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.02196758426725864</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0.01383364200592041</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0353706069290638</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0004382302286103368</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.03149127587676048</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.02554225921630859</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.003061135532334447</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.008138850331306458</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.03218821436166763</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.003365073353052139</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.02152596227824688</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.008917947299778461</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.0002836866769939661</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.01467545889317989</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.02630657143890858</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.02017565444111824</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.004258017055690289</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.05844932049512863</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.02093781717121601</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.01609228551387787</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.03588183596730232</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0322134792804718</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.06236203014850616</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.1232260167598724</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.02116996981203556</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.05564367771148682</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.03213618323206902</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.005072448868304491</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.06007297709584236</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.004525536671280861</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.008660594001412392</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.02762625366449356</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.007141884416341782</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.004851236008107662</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.02474829740822315</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.02304037101566792</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.003959382884204388</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.02599633112549782</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0004935538163408637</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2.317590315215057e-06</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.670445089985151e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.680618879618123e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.857476703065913e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.844889084168244e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.013736775552388e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.892927568609593e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.227772923419252e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.318611783877714e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.169453639704443e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.986700772249606e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.48334927164251e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.290787162768538e-06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.941939086071216e-06</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.464057459088508e-05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.354009214082907e-06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.686430732661393e-05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.259059899894055e-05</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.281302616007451e-06</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.256658262922429e-06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.351104058107012e-06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.717340627597878e-07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.420686541881878e-06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6.812852006987669e-06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.111874664478819e-06</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.516176431934582e-06</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.631860070323455e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.750300948013319e-06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.659258709376445e-06</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>9.488831409498744e-08</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>6.352241143758874e-06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.751837200776208e-06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.178489128506044e-06</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.584917410786147e-06</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.936428245448042e-06</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.028635870170547e-05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.194286025769543e-06</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>9.321824109065346e-06</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2.937812951131491e-06</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.056122750422219e-06</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>9.721257811179385e-06</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.314097739348654e-06</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.863930603780318e-06</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.000228960241657e-06</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.491217062721262e-06</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.304790885114926e-06</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.427160688966978e-05</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.785529992863303e-07</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.267110860680987e-06</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.922117452428211e-06</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.147901614080183e-05</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.486898771778215e-06</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.796722805622267e-06</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.995598833877011e-06</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.659851351287216e-06</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.239346784132067e-05</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.029154736897908e-05</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.545932147768326e-06</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.004586116934661e-06</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.723606821244175e-07</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.820978119823849e-06</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.207439138146583e-06</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.066875483957119e-06</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>3.362863026268315e-06</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.527367996663088e-06</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.748956937168259e-06</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>6.550229045387823e-06</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2.108564700620263e-08</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>3.396064585103886e-07</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>6.998210210440448e-06</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>3.358471985848155e-06</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>3.506102075334638e-10</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>2.84056977761793e-06</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1.015158704831265e-05</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.644050144022913e-06</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1.124729578805272e-06</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.146233327948721e-06</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.535319097456522e-05</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.642600065883016e-06</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>4.342537977208849e-06</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>1.514559244242264e-06</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>4.329696139393491e-07</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>6.340254003589507e-06</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>4.777399226441048e-06</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>1.007547894005256e-06</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>4.832795639231335e-07</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>4.774699391418835e-06</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.044565806296305e-06</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>4.139039049277926e-07</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>9.16329895517265e-07</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>8.214893568947446e-06</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>4.478677510633133e-06</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>5.893127308809198e-06</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>6.627305538131623e-06</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>4.324764631746802e-06</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.157643600890879e-05</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1.688865040705423e-06</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>4.258943590684794e-06</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.747850888023095e-06</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2.056832499874872e-07</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>7.659559742023703e-06</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>5.851217792951502e-06</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>6.108456318543176e-07</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1.4712429674546e-06</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>6.066083642508602e-06</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.219621140080562e-06</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>4.384204999041685e-07</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>7.514349817938637e-07</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3.051879048143746e-06</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.51183830894297e-05</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>2.016452526731882e-06</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>4.06892468163278e-07</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>1.398503172822529e-05</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>8.368455382878892e-06</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>1.348278146906523e-06</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>8.79898107086774e-06</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>8.494537269143621e-07</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>2.09666268347064e-06</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1.894029537652386e-06</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>3.913004547939636e-06</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>1.529235646557936e-06</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>2.744691300904378e-06</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>1.302325586038933e-06</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>8.149159498316294e-07</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>6.495561592601007e-06</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>1.14662395844789e-06</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>1.753983724483987e-06</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>8.982762665254995e-06</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>3.110152647423092e-06</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1.582417326062568e-06</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>5.189627700019628e-06</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.111412348109297e-05</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>1.024387188408582e-06</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>5.282602614897769e-06</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>1.043024099089962e-06</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>1.12255861495214e-06</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>6.231031875358894e-06</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>5.009319465898443e-06</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>1.993926389332046e-06</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>4.046032984206249e-07</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>1.474154259994975e-06</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>3.090414338657865e-06</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>2.052145646302961e-06</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>1.119157786888536e-06</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>2.651258910191245e-06</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>4.001702109235339e-06</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>6.38703625099879e-07</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>3.102069513261085e-06</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>2.09271229323349e-06</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>2.580992486400646e-06</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>4.354672000772553e-08</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>5.337880793376826e-06</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>5.491389856615569e-06</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>7.630347909071133e-07</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>7.571192327304743e-06</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>4.42079999629641e-06</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>3.690012135848519e-07</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>1.054729068528104e-06</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>6.351789124892093e-06</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>6.700799985992489e-07</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>1.287122586290934e-08</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>1.541689584882988e-06</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>3.43943327152374e-08</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>3.988692697021179e-06</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>1.654430661801598e-06</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>1.923021272887127e-06</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>6.443057372962357e-06</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>8.845140087032632e-07</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>5.057842145106406e-07</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>4.243776885459738e-09</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>9.083601071324665e-07</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>4.840736437472515e-06</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>2.880918145820033e-06</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>9.413513453182532e-07</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>1.366917786072008e-05</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>9.449025810681633e-07</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>1.435248123016208e-05</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>9.53545531956479e-06</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>4.315859314374393e-07</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>6.040240805305075e-06</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>4.098799763596617e-06</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>7.970794285938609e-06</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>7.170768640207825e-06</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>2.526187927287538e-06</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>4.36690413607721e-07</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>1.147356897490681e-06</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>1.158067902906623e-06</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>4.54660084869829e-06</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>5.740629376305151e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.05960719287395477</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.02780341170728207</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04670269414782524</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0357217863202095</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02113538421690464</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07376298308372498</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01488727983087301</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.04310496151447296</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01657559908926487</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.04594980925321579</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.03156844899058342</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.06086643412709236</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.03318390622735023</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03951386734843254</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07084452360868454</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.02594067342579365</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05776800215244293</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.02234978415071964</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.008468936197459698</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.0155635317787528</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.009840103797614574</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.0001846929080784321</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.006112066097557545</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.009966376237571239</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.005100454203784466</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.01496886927634478</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.002801601309329271</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.0301448255777359</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.01966597884893417</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.004086069762706757</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.04087955132126808</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02192860469222069</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.02883344516158104</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.007551821880042553</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.008150912821292877</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.007989665493369102</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.02153165452182293</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.02879760786890984</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.0016473145224154</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.00514237629249692</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.02722532860934734</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.01815013401210308</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.01171854604035616</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.001106101786717772</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.002558594802394509</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.009408039972186089</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.07140812277793884</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.004598392173647881</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.01180335879325867</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.0002848284202627838</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.04024860635399818</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.02524511143565178</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.02591551840305328</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.008630902506411076</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.03719185665249825</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.02129564248025417</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.01652001030743122</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.009523655287921429</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.02691672928631306</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.01097960770130157</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.000590895302593708</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.004374671261757612</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.0104203000664711</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.001212812028825283</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.003579833544790745</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.03788931667804718</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.001064762007445097</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.01621417514979839</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.002412874717265368</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.008292006328701973</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.004133628681302071</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.01803180016577244</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.01364377979189157</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.03293862566351891</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.00952286459505558</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.02211758680641651</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.004791690967977047</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.03780372813344002</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.01012599654495716</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.01325027085840702</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.002791075734421611</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.007719161454588175</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.01072140224277973</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.01693377830088139</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.003457712475210428</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.0001941516093211249</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.01778258942067623</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.007843205705285072</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.001280520344153047</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.005519768688827753</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.007125222124159336</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.02204519137740135</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.008911419659852982</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.007432048209011555</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.01506455056369305</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.01251479052007198</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.008947052992880344</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.009532861411571503</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.004038121551275253</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.005511346738785505</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.005537026096135378</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.0127060255035758</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.004551786463707685</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.006847038399428129</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.01866585575044155</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.00327380420640111</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.006945060100406408</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.006645593792200089</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.01591788977384567</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.02317181415855885</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.002384372521191835</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.004425818100571632</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.009045944549143314</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.02606243453919888</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.01204392965883017</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.00750207481905818</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.004948446527123451</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.008976960554718971</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.01247892528772354</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.00287984311580658</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.01024981308728456</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.02187534235417843</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.007321880199015141</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.004626309499144554</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.01203123480081558</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.02219553850591183</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.004908563569188118</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.02005135267972946</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.006493887864053249</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>4.072301089763641e-05</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.004207732155919075</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.00090944510884583</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.005782867316156626</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.02101924456655979</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.006611899472773075</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.02230079472064972</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.005321313161402941</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.01347710750997066</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.01135503314435482</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.01363030541688204</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.003043262520805001</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.004845907445997</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.003518717829138041</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.007511951494961977</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.003164906054735184</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.004585385788232088</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.002965898253023624</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.01952914521098137</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.001303635537624359</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.03139570727944374</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.005152679979801178</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.008402591571211815</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.02298235893249512</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.006635698489844799</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.01224765833467245</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.01349254325032234</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.003057199064642191</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.001438263570889831</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.01979684270918369</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.005366489291191101</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.001658332766965032</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.004100308753550053</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.008244605734944344</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.01004291884601116</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.005618700757622719</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.00887229572981596</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.00535562913864851</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.03191346302628517</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.008585616014897823</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.00703879352658987</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.0130362780764699</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.008904105983674526</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.008066987618803978</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.005052676424384117</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.02608144842088223</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.05507545173168182</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.007030142936855555</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.005486207082867622</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.005633563734591007</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.03728331997990608</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.01077385060489178</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.001831969246268272</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.02138781175017357</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.03314309194684029</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.005098867230117321</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.001465114066377282</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.002388516208156943</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.002451678505167365</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.01264014188200235</v>
       </c>
     </row>
   </sheetData>
